--- a/artfynd/A 17836-2025 artfynd.xlsx
+++ b/artfynd/A 17836-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>24765</v>
       </c>
       <c r="B2" t="n">
-        <v>57586</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476658.4689364026</v>
+        <v>476658</v>
       </c>
       <c r="R2" t="n">
-        <v>6406965.296022132</v>
+        <v>6406965</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2005-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68175974</v>
+        <v>68175917</v>
       </c>
       <c r="B3" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +811,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,21 +819,24 @@
           <t>ex.</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>49, Sm</t>
+          <t>Ost om Karsäng (2 st gölar), södra, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476683.4716965213</v>
+        <v>476634</v>
       </c>
       <c r="R3" t="n">
-        <v>6406949.697597333</v>
+        <v>6406804</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,22 +863,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-05-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-05-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-05-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +888,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Stahre</t>
+          <t>Josefine Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -926,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68176208</v>
+        <v>68175973</v>
       </c>
       <c r="B4" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,17 +927,31 @@
           <t>(Laurenti, 1768)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ost om Karsäng (2 st gölar), norra, Sm</t>
+          <t>49, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476682.144557116</v>
+        <v>476683</v>
       </c>
       <c r="R4" t="n">
-        <v>6406904.943186879</v>
+        <v>6406950</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,22 +978,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1999-05-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1999-05-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1003,128 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Mattias Stare</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Salamander inventering i Jönköpings län</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>68175915</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ost om Karsäng (2 st gölar), södra, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476634</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6406804</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järsnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1999-05-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1999-05-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Anna Isaksson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Josefine Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Salamander inventering i Jönköpings län</t>
         </is>

--- a/artfynd/A 17836-2025 artfynd.xlsx
+++ b/artfynd/A 17836-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Större vattensalamander I Jönköpings län 2004-2005</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/24765</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Salamander inventering i Jönköpings län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68175917</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>Salamander inventering i Jönköpings län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68175973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,8 +1149,19 @@
           <t>Salamander inventering i Jönköpings län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68175915</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>